--- a/tabular/genus/dependo-refseq-feature-locations.xlsx
+++ b/tabular/genus/dependo-refseq-feature-locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BC9D55-A4A8-FC43-AD5F-4A40147E6B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1F3E3C-B33C-5B49-97C5-8DB158D36392}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14620" yWindow="1740" windowWidth="22440" windowHeight="23460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="500" windowWidth="22440" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -177,30 +177,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9999FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1951,26 +1933,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1737">
     <cellStyle name="Followed Hyperlink" xfId="1" builtinId="9" hidden="1"/>
@@ -3711,7 +3692,48 @@
     <cellStyle name="Hyperlink" xfId="1735" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3722,6 +3744,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09A85CD8-46A4-C34A-BEA7-1E30186DFB95}" name="Table1" displayName="Table1" ref="A1:D72" totalsRowShown="0" dataDxfId="0">
+  <autoFilter ref="A1:D72" xr:uid="{22E362A8-AB6C-4C42-9509-0BAFBEF5D57B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F6E119D3-A71D-784F-B038-EAB793CE8FD3}" name="referenceName" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{CB0F1F5A-A056-8747-A00A-FD2C53CA5485}" name="featureName" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{9985E7FE-249C-2147-86F9-AFB5A4B03210}" name="startNT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{CEEC495A-2B36-824F-8017-36D433910228}" name="endNT" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4052,17 +4087,17 @@
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
     <col min="2" max="2" width="16.1640625" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12" style="8" customWidth="1"/>
+    <col min="4" max="4" width="12" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.83203125" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -4073,27 +4108,27 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>4726</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>318</v>
       </c>
       <c r="D3" s="7">
@@ -4101,13 +4136,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>2209</v>
       </c>
       <c r="D4" s="7">
@@ -4115,13 +4150,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="7">
@@ -4129,13 +4164,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>317</v>
       </c>
       <c r="D6" s="7">
@@ -4143,13 +4178,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="1">
         <v>2208</v>
       </c>
       <c r="D7" s="7">
@@ -4157,13 +4192,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="7">
@@ -4171,13 +4206,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="1">
         <v>372</v>
       </c>
       <c r="D9" s="7">
@@ -4185,13 +4220,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="1">
         <v>2260</v>
       </c>
       <c r="D10" s="7">
@@ -4199,13 +4234,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="7">
@@ -4213,13 +4248,13 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="1">
         <v>359</v>
       </c>
       <c r="D12" s="7">
@@ -4227,13 +4262,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="1">
         <v>2207</v>
       </c>
       <c r="D13" s="7">
@@ -4241,13 +4276,13 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" s="7">
@@ -4255,13 +4290,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="1">
         <v>320</v>
       </c>
       <c r="D15" s="7">
@@ -4269,13 +4304,13 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="1">
         <v>2208</v>
       </c>
       <c r="D16" s="7">
@@ -4283,13 +4318,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="7">
@@ -4297,13 +4332,13 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="1">
         <v>334</v>
       </c>
       <c r="D18" s="7">
@@ -4311,13 +4346,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="1">
         <v>2222</v>
       </c>
       <c r="D19" s="7">
@@ -4325,13 +4360,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="7">
@@ -4339,13 +4374,13 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="1">
         <v>227</v>
       </c>
       <c r="D21" s="7">
@@ -4353,13 +4388,13 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="1">
         <v>2121</v>
       </c>
       <c r="D22" s="7">
@@ -4367,13 +4402,13 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="7">
@@ -4381,13 +4416,13 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="1">
         <v>228</v>
       </c>
       <c r="D24" s="7">
@@ -4395,13 +4430,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="1">
         <v>2116</v>
       </c>
       <c r="D25" s="7">
@@ -4409,13 +4444,13 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="1">
         <v>1</v>
       </c>
       <c r="D26" s="7">
@@ -4423,13 +4458,13 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="1">
         <v>1</v>
       </c>
       <c r="D27" s="7">
@@ -4437,13 +4472,13 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="1">
         <v>1886</v>
       </c>
       <c r="D28" s="7">
@@ -4451,13 +4486,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" s="7">
@@ -4465,13 +4500,13 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="1">
         <v>1</v>
       </c>
       <c r="D30" s="7">
@@ -4479,13 +4514,13 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="1">
         <v>1886</v>
       </c>
       <c r="D31" s="7">
@@ -4493,13 +4528,13 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="1">
         <v>1</v>
       </c>
       <c r="D32" s="7">
@@ -4507,13 +4542,13 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="1">
         <v>103</v>
       </c>
       <c r="D33" s="7">
@@ -4521,13 +4556,13 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="1">
         <v>1985</v>
       </c>
       <c r="D34" s="7">
@@ -4535,13 +4570,13 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="7">
@@ -4549,13 +4584,13 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="1">
         <v>324</v>
       </c>
       <c r="D36" s="7">
@@ -4563,13 +4598,13 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="1">
         <v>2030</v>
       </c>
       <c r="D37" s="7">
@@ -4577,13 +4612,13 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="1">
         <v>1</v>
       </c>
       <c r="D38" s="7">
@@ -4591,13 +4626,13 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="1">
         <v>347</v>
       </c>
       <c r="D39" s="7">
@@ -4605,13 +4640,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="1">
         <v>2195</v>
       </c>
       <c r="D40" s="7">
@@ -4619,13 +4654,13 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="1">
         <v>1</v>
       </c>
       <c r="D41" s="7">
@@ -4633,13 +4668,13 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="1">
         <v>537</v>
       </c>
       <c r="D42" s="7">
@@ -4647,13 +4682,13 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="1">
         <v>2439</v>
       </c>
       <c r="D43" s="7">
@@ -4661,13 +4696,13 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="1">
         <v>1</v>
       </c>
       <c r="D44" s="7">
@@ -4675,13 +4710,13 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="7">
@@ -4689,10 +4724,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="7">
@@ -4703,27 +4738,27 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C47" s="7">
         <v>4678</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>5106</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="7">
@@ -4731,13 +4766,13 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="1">
         <v>548</v>
       </c>
       <c r="D49" s="7">
@@ -4745,13 +4780,13 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="1">
         <v>2450</v>
       </c>
       <c r="D50" s="7">
@@ -4759,27 +4794,27 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="1">
         <v>1</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="1">
         <v>547</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="1">
         <v>1</v>
       </c>
       <c r="D52" s="7">
@@ -4787,10 +4822,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="7">
@@ -4801,27 +4836,27 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C54" s="7">
         <v>4663</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>5132</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="1">
         <v>1</v>
       </c>
       <c r="D55" s="7">
@@ -4829,240 +4864,240 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="1">
         <v>335</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="1">
         <v>2206</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="1">
         <v>2223</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="1">
         <v>4433</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="1">
         <v>1</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <v>4339</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="1">
         <v>314</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="1">
         <v>2032</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="1">
         <v>2049</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="1">
         <v>4280</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="1">
         <v>1</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="1">
         <v>2977</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="1">
         <v>3</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="1">
         <v>764</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="1">
         <v>1188</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="1">
         <v>2930</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="1">
         <v>1</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="1">
         <v>4286</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="1">
         <v>200</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="1">
         <v>2041</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="1">
         <v>2059</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="1">
         <v>4233</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="1">
         <v>1</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="1">
         <v>4395</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="1">
         <v>291</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="1">
         <v>2093</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="1">
         <v>2124</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="1">
         <v>4280</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="1">
         <v>1</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="1">
         <v>3472</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="1">
         <v>1</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="1">
         <v>1287</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="1">
         <v>1298</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="1">
         <v>3472</v>
       </c>
     </row>
@@ -5097,12 +5132,12 @@
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="1"/>
-      <c r="D80" s="9"/>
+      <c r="D80" s="4"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="1"/>
-      <c r="D81" s="9"/>
+      <c r="D81" s="4"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
@@ -5553,15 +5588,15 @@
     </row>
     <row r="1251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C1251" s="2"/>
-      <c r="D1251" s="9"/>
+      <c r="D1251" s="4"/>
     </row>
     <row r="1252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C1252" s="2"/>
-      <c r="D1252" s="9"/>
+      <c r="D1252" s="4"/>
     </row>
     <row r="1253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C1253" s="2"/>
-      <c r="D1253" s="9"/>
+      <c r="D1253" s="4"/>
     </row>
     <row r="1255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1255" s="2"/>
@@ -5661,26 +5696,26 @@
     </row>
     <row r="1433" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C1433" s="2"/>
-      <c r="D1433" s="9"/>
+      <c r="D1433" s="4"/>
     </row>
     <row r="1434" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B1434" s="2"/>
       <c r="C1434" s="2"/>
-      <c r="D1434" s="9"/>
+      <c r="D1434" s="4"/>
     </row>
     <row r="1435" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B1435" s="2"/>
       <c r="C1435" s="2"/>
-      <c r="D1435" s="9"/>
+      <c r="D1435" s="4"/>
     </row>
     <row r="1436" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B1436" s="2"/>
       <c r="C1436" s="2"/>
-      <c r="D1436" s="9"/>
+      <c r="D1436" s="4"/>
     </row>
     <row r="1437" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C1437" s="2"/>
-      <c r="D1437" s="9"/>
+      <c r="D1437" s="4"/>
     </row>
     <row r="1500" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1500" s="2"/>
@@ -5697,6 +5732,9 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
